--- a/consent_forms/026_sugaring_intake_form--consent_forms.xlsx
+++ b/consent_forms/026_sugaring_intake_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Medical History 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Medical History 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vaccination History</t>
+          <t>Medical History 3 Vaccination History</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Previous Surgeries</t>
+          <t>Medical History 4 Previous Surgeries</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Breastfeeding</t>
+          <t>Medical History 6 Breastfeeding</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other Medical History</t>
+          <t>Medical History 7 Other Medical History</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Allergies</t>
+          <t>Allergies (2)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Allergies</t>
+          <t>Allergies Allergies</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1121,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
@@ -1477,29 +1477,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>allergic</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Allergic</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>medical_history_2_medical_tests_choices</t>
+          <t>medical_history_3_vaccination_history_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>vaccinated</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Vaccinated</t>
         </is>
       </c>
     </row>
@@ -1511,29 +1511,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>vaccinated</t>
+          <t>not_vaccinated</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vaccinated</t>
+          <t>Not Vaccinated</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>medical_history_3_vaccination_history_choices</t>
+          <t>medical_history_4_previous_surgeries_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>not_vaccinated</t>
+          <t>previous_surgery_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Not Vaccinated</t>
+          <t>Previous Surgery 1</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>previous_surgery_1</t>
+          <t>previous_surgery_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Previous Surgery 1</t>
+          <t>Previous Surgery 2</t>
         </is>
       </c>
     </row>
@@ -1562,29 +1562,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>previous_surgery_2</t>
+          <t>previous_surgery_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Previous Surgery 2</t>
+          <t>Previous Surgery 3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>medical_history_4_previous_surgeries_choices</t>
+          <t>medical_history_5_pregnant_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>previous_surgery_3</t>
+          <t>pregnant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Previous Surgery 3</t>
+          <t>Pregnant</t>
         </is>
       </c>
     </row>
@@ -1596,29 +1596,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>pregnant</t>
+          <t>not_pregnant</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pregnant</t>
+          <t>Not Pregnant</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>medical_history_5_pregnant_choices</t>
+          <t>medical_history_6_breastfeeding_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>not_pregnant</t>
+          <t>breastfeeding</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Not Pregnant</t>
+          <t>Breastfeeding</t>
         </is>
       </c>
     </row>
@@ -1630,29 +1630,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>breastfeeding</t>
+          <t>not_breastfeeding</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Breastfeeding</t>
+          <t>Not Breastfeeding</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>medical_history_6_breastfeeding_choices</t>
+          <t>medications_medication_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>not_breastfeeding</t>
+          <t>medication_1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Not Breastfeeding</t>
+          <t>Medication 1</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>medication_1</t>
+          <t>medication_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Medication 1</t>
+          <t>Medication 2</t>
         </is>
       </c>
     </row>
@@ -1681,29 +1681,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>medication_2</t>
+          <t>medication_3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Medication 2</t>
+          <t>Medication 3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>medications_medication_choices</t>
+          <t>allergies_allergies_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>medication_3</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Medication 3</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -1715,27 +1715,10 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>no_allergies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
-        <is>
-          <t>Allergies</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>allergies_allergies_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>no_allergies</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
         <is>
           <t>No Allergies</t>
         </is>
